--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-08.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-08.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="282">
   <si>
     <t>Date: 2024-07-08</t>
   </si>
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Dakshinkali Investment Securities Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Vision Securities Pvt.Limited</t>
-  </si>
-  <si>
     <t>Dynamic Money Managers Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Sumeru Securities Pvt.Limited</t>
+    <t>Linch Stock Market Limited</t>
+  </si>
+  <si>
+    <t>Sani Securities Company Limited</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
     <t>44</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>408,304,150.04</t>
-  </si>
-  <si>
-    <t>351,496,884.6</t>
-  </si>
-  <si>
-    <t>334,026,127.1</t>
-  </si>
-  <si>
-    <t>326,603,974.8</t>
-  </si>
-  <si>
-    <t>306,010,534.14</t>
-  </si>
-  <si>
-    <t>286,730,086.5</t>
-  </si>
-  <si>
-    <t>283,025,714.1</t>
-  </si>
-  <si>
-    <t>195,934,547.85</t>
-  </si>
-  <si>
-    <t>98,566,212.3</t>
-  </si>
-  <si>
-    <t>179,792,593.9</t>
-  </si>
-  <si>
-    <t>209,059,583.8</t>
-  </si>
-  <si>
-    <t>162,300,453.19</t>
-  </si>
-  <si>
-    <t>181,961,244.7</t>
-  </si>
-  <si>
-    <t>112,985,418.6</t>
-  </si>
-  <si>
-    <t>212,369,602.2</t>
-  </si>
-  <si>
-    <t>252,930,672.3</t>
-  </si>
-  <si>
-    <t>154,233,533.19</t>
-  </si>
-  <si>
-    <t>117,544,391.0</t>
-  </si>
-  <si>
-    <t>143,710,080.94</t>
-  </si>
-  <si>
-    <t>104,768,841.8</t>
-  </si>
-  <si>
-    <t>170,040,295.5</t>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>478,518,543.75</t>
+  </si>
+  <si>
+    <t>378,165,744.44</t>
+  </si>
+  <si>
+    <t>345,165,219.1</t>
+  </si>
+  <si>
+    <t>301,236,171.6</t>
+  </si>
+  <si>
+    <t>292,739,513.0</t>
+  </si>
+  <si>
+    <t>280,244,856.3</t>
+  </si>
+  <si>
+    <t>277,342,617.7</t>
+  </si>
+  <si>
+    <t>239,330,868.05</t>
+  </si>
+  <si>
+    <t>206,088,191.7</t>
+  </si>
+  <si>
+    <t>168,828,670.69</t>
+  </si>
+  <si>
+    <t>130,591,766.1</t>
+  </si>
+  <si>
+    <t>147,266,748.1</t>
+  </si>
+  <si>
+    <t>130,229,965.3</t>
+  </si>
+  <si>
+    <t>148,012,149.6</t>
+  </si>
+  <si>
+    <t>239,187,675.7</t>
+  </si>
+  <si>
+    <t>172,077,552.74</t>
+  </si>
+  <si>
+    <t>176,336,548.4</t>
+  </si>
+  <si>
+    <t>170,644,405.5</t>
+  </si>
+  <si>
+    <t>145,472,764.9</t>
+  </si>
+  <si>
+    <t>150,014,891.0</t>
+  </si>
+  <si>
+    <t>129,330,468.1</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,469 +182,460 @@
     <t>NRN</t>
   </si>
   <si>
-    <t>38,124,923.0</t>
+    <t>60,178,869.0</t>
   </si>
   <si>
     <t>FOWAD</t>
   </si>
   <si>
-    <t>22,056,761.2</t>
+    <t>22,473,365.9</t>
+  </si>
+  <si>
+    <t>SAMAJ</t>
+  </si>
+  <si>
+    <t>6,727,444.0</t>
+  </si>
+  <si>
+    <t>MKHL</t>
+  </si>
+  <si>
+    <t>6,289,275.6</t>
   </si>
   <si>
     <t>LBBL</t>
   </si>
   <si>
-    <t>14,645,817.2</t>
-  </si>
-  <si>
-    <t>GMFBS</t>
-  </si>
-  <si>
-    <t>5,581,516.3</t>
-  </si>
-  <si>
-    <t>SHPC</t>
-  </si>
-  <si>
-    <t>4,596,287.0</t>
+    <t>6,143,017.2</t>
+  </si>
+  <si>
+    <t>SBI</t>
+  </si>
+  <si>
+    <t>13,069,410.4</t>
+  </si>
+  <si>
+    <t>NRM</t>
+  </si>
+  <si>
+    <t>12,428,410.2</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>10,259,966.0</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>7,565,902.0</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>7,018,672.4</t>
+  </si>
+  <si>
+    <t>10,412,133.0</t>
+  </si>
+  <si>
+    <t>ICFC</t>
+  </si>
+  <si>
+    <t>9,705,029.1</t>
+  </si>
+  <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>7,230,920.0</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>7,082,985.5</t>
+  </si>
+  <si>
+    <t>4,673,650.7</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>18,230,872.0</t>
+  </si>
+  <si>
+    <t>OHL</t>
+  </si>
+  <si>
+    <t>9,127,932.5</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>7,341,757.7</t>
+  </si>
+  <si>
+    <t>5,650,072.0</t>
+  </si>
+  <si>
+    <t>NLG</t>
+  </si>
+  <si>
+    <t>4,666,280.0</t>
+  </si>
+  <si>
+    <t>MSLB</t>
+  </si>
+  <si>
+    <t>14,067,183.6</t>
+  </si>
+  <si>
+    <t>SPIL</t>
+  </si>
+  <si>
+    <t>8,195,109.0</t>
+  </si>
+  <si>
+    <t>SWBBL</t>
+  </si>
+  <si>
+    <t>5,533,786.2</t>
+  </si>
+  <si>
+    <t>SMJC</t>
+  </si>
+  <si>
+    <t>5,371,605.0</t>
+  </si>
+  <si>
+    <t>4,425,999.0</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>46,810,454.4</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>17,134,509.0</t>
   </si>
   <si>
     <t>GFCL</t>
   </si>
   <si>
-    <t>7,640,598.5</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>5,751,613.4</t>
-  </si>
-  <si>
-    <t>NLG</t>
-  </si>
-  <si>
-    <t>4,635,000.0</t>
-  </si>
-  <si>
-    <t>EBLD86</t>
-  </si>
-  <si>
-    <t>3,880,400.0</t>
-  </si>
-  <si>
-    <t>CFCL</t>
-  </si>
-  <si>
-    <t>3,709,445.0</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>24,208,320.0</t>
-  </si>
-  <si>
-    <t>EDBL</t>
-  </si>
-  <si>
-    <t>15,475,783.0</t>
-  </si>
-  <si>
-    <t>ILI</t>
-  </si>
-  <si>
-    <t>9,841,819.0</t>
-  </si>
-  <si>
-    <t>9,307,133.0</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>6,951,905.5</t>
-  </si>
-  <si>
-    <t>NLICL</t>
-  </si>
-  <si>
-    <t>54,522,150.0</t>
-  </si>
-  <si>
-    <t>50,546,270.0</t>
-  </si>
-  <si>
-    <t>SPIL</t>
-  </si>
-  <si>
-    <t>42,764,009.0</t>
-  </si>
-  <si>
-    <t>JBLB</t>
-  </si>
-  <si>
-    <t>8,072,908.3</t>
-  </si>
-  <si>
-    <t>NICA</t>
-  </si>
-  <si>
-    <t>6,111,613.1</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>19,932,092.0</t>
-  </si>
-  <si>
-    <t>BEDC</t>
-  </si>
-  <si>
-    <t>7,780,628.0</t>
-  </si>
-  <si>
-    <t>6,415,167.3</t>
-  </si>
-  <si>
-    <t>MKCL</t>
-  </si>
-  <si>
-    <t>6,407,137.0</t>
-  </si>
-  <si>
-    <t>5,808,327.0</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>40,182,566.2</t>
-  </si>
-  <si>
-    <t>ACLBSL</t>
-  </si>
-  <si>
-    <t>24,143,639.0</t>
-  </si>
-  <si>
-    <t>RADHI</t>
-  </si>
-  <si>
-    <t>15,156,837.0</t>
-  </si>
-  <si>
-    <t>MSLB</t>
-  </si>
-  <si>
-    <t>14,067,183.6</t>
-  </si>
-  <si>
-    <t>4,898,712.0</t>
-  </si>
-  <si>
-    <t>TAMOR</t>
-  </si>
-  <si>
-    <t>28,043,228.0</t>
-  </si>
-  <si>
-    <t>22,679,700.3</t>
-  </si>
-  <si>
-    <t>14,236,130.7</t>
-  </si>
-  <si>
-    <t>BNHC</t>
-  </si>
-  <si>
-    <t>8,001,586.4</t>
-  </si>
-  <si>
-    <t>LBLD86</t>
-  </si>
-  <si>
-    <t>5,810,508.0</t>
+    <t>16,291,645.3</t>
+  </si>
+  <si>
+    <t>4,188,199.0</t>
+  </si>
+  <si>
+    <t>1,721,034.1</t>
+  </si>
+  <si>
+    <t>9,823,057.4</t>
+  </si>
+  <si>
+    <t>SADBL</t>
+  </si>
+  <si>
+    <t>5,572,044.6</t>
+  </si>
+  <si>
+    <t>5,416,018.5</t>
+  </si>
+  <si>
+    <t>5,353,738.0</t>
+  </si>
+  <si>
+    <t>VLBS</t>
+  </si>
+  <si>
+    <t>5,303,403.59</t>
   </si>
   <si>
     <t>Sell Amount</t>
   </si>
   <si>
+    <t>28,878,397.6</t>
+  </si>
+  <si>
     <t>MEN</t>
   </si>
   <si>
-    <t>23,482,051.0</t>
-  </si>
-  <si>
-    <t>PROFL</t>
-  </si>
-  <si>
-    <t>23,453,801.2</t>
-  </si>
-  <si>
-    <t>21,836,621.5</t>
-  </si>
-  <si>
-    <t>13,118,137.0</t>
-  </si>
-  <si>
-    <t>SAMAJ</t>
-  </si>
-  <si>
-    <t>11,117,065.0</t>
-  </si>
-  <si>
-    <t>110,477,274.0</t>
-  </si>
-  <si>
-    <t>40,110,656.2</t>
+    <t>23,488,420.0</t>
+  </si>
+  <si>
+    <t>21,928,329.5</t>
+  </si>
+  <si>
+    <t>15,423,429.0</t>
   </si>
   <si>
     <t>NTC</t>
   </si>
   <si>
-    <t>22,008,388.0</t>
-  </si>
-  <si>
-    <t>PCBL</t>
-  </si>
-  <si>
-    <t>5,940,343.6</t>
+    <t>6,540,114.7</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>14,361,123.4</t>
+  </si>
+  <si>
+    <t>ILBS</t>
+  </si>
+  <si>
+    <t>4,475,122.7</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>4,416,164.5</t>
+  </si>
+  <si>
+    <t>RNLI</t>
+  </si>
+  <si>
+    <t>4,121,553.4</t>
+  </si>
+  <si>
+    <t>4,060,109.4</t>
+  </si>
+  <si>
+    <t>7,559,403.0</t>
+  </si>
+  <si>
+    <t>NIFRA</t>
+  </si>
+  <si>
+    <t>7,109,412.5</t>
+  </si>
+  <si>
+    <t>SNLI</t>
+  </si>
+  <si>
+    <t>6,689,344.6</t>
+  </si>
+  <si>
+    <t>6,420,484.0</t>
+  </si>
+  <si>
+    <t>5,850,944.1</t>
+  </si>
+  <si>
+    <t>49,469,126.2</t>
+  </si>
+  <si>
+    <t>14,618,403.0</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>5,468,863.2</t>
+  </si>
+  <si>
+    <t>5,101,458.7</t>
   </si>
   <si>
     <t>NRIC</t>
   </si>
   <si>
-    <t>3,855,203.1</t>
-  </si>
-  <si>
-    <t>CKHL</t>
-  </si>
-  <si>
-    <t>11,909,830.0</t>
-  </si>
-  <si>
-    <t>11,375,678.0</t>
-  </si>
-  <si>
-    <t>5,851,843.0</t>
-  </si>
-  <si>
-    <t>ICFC</t>
-  </si>
-  <si>
-    <t>5,487,877.0</t>
+    <t>5,042,905.3</t>
+  </si>
+  <si>
+    <t>14,784,501.1</t>
   </si>
   <si>
     <t>SINDU</t>
   </si>
   <si>
-    <t>4,832,864.5</t>
-  </si>
-  <si>
-    <t>35,822,160.9</t>
-  </si>
-  <si>
-    <t>9,260,193.0</t>
+    <t>10,912,500.0</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>7,988,930.1</t>
+  </si>
+  <si>
+    <t>7,783,310.3</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>7,059,668.0</t>
+  </si>
+  <si>
+    <t>71,905,972.2</t>
+  </si>
+  <si>
+    <t>19,347,714.2</t>
+  </si>
+  <si>
+    <t>8,218,688.8</t>
+  </si>
+  <si>
+    <t>2,482,048.79</t>
+  </si>
+  <si>
+    <t>ENL</t>
+  </si>
+  <si>
+    <t>2,137,186.0</t>
+  </si>
+  <si>
+    <t>10,736,528.5</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>8,019,943.0</t>
+  </si>
+  <si>
+    <t>MPFL</t>
+  </si>
+  <si>
+    <t>5,476,116.0</t>
+  </si>
+  <si>
+    <t>CITY</t>
+  </si>
+  <si>
+    <t>4,015,363.0</t>
+  </si>
+  <si>
+    <t>3,941,533.9</t>
+  </si>
+  <si>
+    <t>Top Traded Stocks</t>
+  </si>
+  <si>
+    <t>Turnover (Rs.)</t>
+  </si>
+  <si>
+    <t>Sub Indices</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Percentage (%)</t>
+  </si>
+  <si>
+    <t>315,936,900.1</t>
+  </si>
+  <si>
+    <t>152,019,809.8</t>
   </si>
   <si>
     <t>CHDC</t>
   </si>
   <si>
-    <t>7,278,011.0</t>
-  </si>
-  <si>
-    <t>NUBL</t>
-  </si>
-  <si>
-    <t>6,093,000.0</t>
-  </si>
-  <si>
-    <t>KMCDB</t>
-  </si>
-  <si>
-    <t>5,709,036.3</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>14,306,227.6</t>
-  </si>
-  <si>
-    <t>5,790,103.9</t>
-  </si>
-  <si>
-    <t>ILBS</t>
-  </si>
-  <si>
-    <t>4,452,303.7</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>4,416,164.5</t>
-  </si>
-  <si>
-    <t>NRM</t>
-  </si>
-  <si>
-    <t>3,906,568.4</t>
-  </si>
-  <si>
-    <t>9,266,010.0</t>
-  </si>
-  <si>
-    <t>7,855,948.0</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>7,586,650.1</t>
-  </si>
-  <si>
-    <t>7,560,003.0</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>6,962,468.0</t>
-  </si>
-  <si>
-    <t>52,629,692.0</t>
-  </si>
-  <si>
-    <t>48,038,240.0</t>
-  </si>
-  <si>
-    <t>STC</t>
-  </si>
-  <si>
-    <t>6,852,221.3</t>
-  </si>
-  <si>
-    <t>6,269,659.0</t>
-  </si>
-  <si>
-    <t>Top Traded Stocks</t>
-  </si>
-  <si>
-    <t>Turnover (Rs.)</t>
-  </si>
-  <si>
-    <t>Sub Indices</t>
-  </si>
-  <si>
-    <t>Turnover</t>
-  </si>
-  <si>
-    <t>Percentage (%)</t>
-  </si>
-  <si>
-    <t>161,837,638.8</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>161,337,089.6</t>
-  </si>
-  <si>
-    <t>140,839,068.5</t>
-  </si>
-  <si>
-    <t>116,569,089.3</t>
-  </si>
-  <si>
-    <t>83,748,132.4</t>
+    <t>89,626,344.2</t>
+  </si>
+  <si>
+    <t>82,276,993.2</t>
+  </si>
+  <si>
+    <t>81,494,384.3</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,013,754,694.0</t>
+    <t>1,108,586,578.4</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>701,945,281.1</t>
+    <t>728,809,568.2</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>696,693,934.3</t>
+    <t>562,304,703.1</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>577,801,004.1</t>
+    <t>550,619,162.6</t>
+  </si>
+  <si>
+    <t>Investment</t>
+  </si>
+  <si>
+    <t>537,776,038.29</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>424,849,038.1</t>
-  </si>
-  <si>
-    <t>Investment</t>
-  </si>
-  <si>
-    <t>299,705,526.1</t>
+    <t>449,088,621.2</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>220,601,183.3</t>
+    <t>218,315,035.6</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>124,747,636.2</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>70,575,345.3</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>186,177,020.4</t>
-  </si>
-  <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>90,023,663.3</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>53,422,045.5</t>
+    <t>64,465,264.5</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>54,498,016.5</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>33,131,226.1</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>49,516,942.5</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>34,869,372.6</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>31,725,934.1</t>
+    <t>32,087,448.9</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>8,225,796.46</t>
+    <t>9,103,920.46</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -662,208 +653,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>41,841,009.5</t>
-  </si>
-  <si>
-    <t>37,821,218.0</t>
-  </si>
-  <si>
-    <t>31,395,635.3</t>
-  </si>
-  <si>
-    <t>28,228,412.1</t>
-  </si>
-  <si>
-    <t>23,352,725.3</t>
-  </si>
-  <si>
-    <t>20,110,678.6</t>
-  </si>
-  <si>
-    <t>18,712,006.5</t>
-  </si>
-  <si>
-    <t>11,378,477.2</t>
-  </si>
-  <si>
-    <t>11,139,940.2</t>
-  </si>
-  <si>
-    <t>10,081,731.0</t>
-  </si>
-  <si>
-    <t>48,816,902.2</t>
-  </si>
-  <si>
-    <t>47,468,288.1</t>
-  </si>
-  <si>
-    <t>21,202,537.0</t>
-  </si>
-  <si>
-    <t>18,920,485.5</t>
-  </si>
-  <si>
-    <t>17,527,867.7</t>
-  </si>
-  <si>
-    <t>58,513,753.7</t>
-  </si>
-  <si>
-    <t>54,581,750.0</t>
-  </si>
-  <si>
-    <t>51,344,998.0</t>
-  </si>
-  <si>
-    <t>14,276,493.6</t>
-  </si>
-  <si>
-    <t>7,284,810.2</t>
-  </si>
-  <si>
-    <t>41,184,560.4</t>
-  </si>
-  <si>
-    <t>27,362,300.1</t>
-  </si>
-  <si>
-    <t>23,237,136.2</t>
-  </si>
-  <si>
-    <t>17,584,876.7</t>
-  </si>
-  <si>
-    <t>13,116,255.1</t>
-  </si>
-  <si>
-    <t>91,808,994.4</t>
-  </si>
-  <si>
-    <t>22,506,316.6</t>
-  </si>
-  <si>
-    <t>21,661,091.7</t>
-  </si>
-  <si>
-    <t>14,247,037.4</t>
-  </si>
-  <si>
-    <t>7,543,592.8</t>
-  </si>
-  <si>
-    <t>40,995,491.79</t>
-  </si>
-  <si>
-    <t>25,063,873.3</t>
-  </si>
-  <si>
-    <t>11,885,793.1</t>
-  </si>
-  <si>
-    <t>6,805,880.2</t>
-  </si>
-  <si>
-    <t>42,635,643.0</t>
-  </si>
-  <si>
-    <t>42,138,442.0</t>
-  </si>
-  <si>
-    <t>41,575,743.2</t>
-  </si>
-  <si>
-    <t>35,512,565.29</t>
-  </si>
-  <si>
-    <t>17,255,505.6</t>
-  </si>
-  <si>
-    <t>114,121,586.6</t>
-  </si>
-  <si>
-    <t>43,664,450.0</t>
-  </si>
-  <si>
-    <t>25,863,591.1</t>
-  </si>
-  <si>
-    <t>15,720,940.5</t>
-  </si>
-  <si>
-    <t>13,652,127.0</t>
-  </si>
-  <si>
-    <t>34,187,168.0</t>
-  </si>
-  <si>
-    <t>32,068,603.1</t>
-  </si>
-  <si>
-    <t>28,578,161.3</t>
-  </si>
-  <si>
-    <t>20,752,813.0</t>
-  </si>
-  <si>
-    <t>18,781,230.39</t>
-  </si>
-  <si>
-    <t>55,612,814.7</t>
-  </si>
-  <si>
-    <t>22,978,442.3</t>
-  </si>
-  <si>
-    <t>10,115,646.6</t>
-  </si>
-  <si>
-    <t>7,738,439.9</t>
-  </si>
-  <si>
-    <t>5,588,821.3</t>
-  </si>
-  <si>
-    <t>46,675,830.1</t>
-  </si>
-  <si>
-    <t>26,287,028.1</t>
-  </si>
-  <si>
-    <t>17,281,405.7</t>
-  </si>
-  <si>
-    <t>14,991,888.2</t>
-  </si>
-  <si>
-    <t>14,216,348.4</t>
-  </si>
-  <si>
-    <t>35,263,071.4</t>
-  </si>
-  <si>
-    <t>20,745,531.39</t>
-  </si>
-  <si>
-    <t>12,225,773.8</t>
-  </si>
-  <si>
-    <t>10,227,989.5</t>
-  </si>
-  <si>
-    <t>6,636,025.8</t>
-  </si>
-  <si>
-    <t>70,521,143.7</t>
-  </si>
-  <si>
-    <t>61,029,602.6</t>
-  </si>
-  <si>
-    <t>8,788,745.19</t>
-  </si>
-  <si>
-    <t>7,781,573.7</t>
+    <t>66,634,868.3</t>
+  </si>
+  <si>
+    <t>45,493,178.4</t>
+  </si>
+  <si>
+    <t>39,781,666.1</t>
+  </si>
+  <si>
+    <t>27,034,561.6</t>
+  </si>
+  <si>
+    <t>24,318,178.3</t>
+  </si>
+  <si>
+    <t>64,702,224.5</t>
+  </si>
+  <si>
+    <t>30,844,947.6</t>
+  </si>
+  <si>
+    <t>23,712,135.5</t>
+  </si>
+  <si>
+    <t>20,362,252.89</t>
+  </si>
+  <si>
+    <t>16,420,373.6</t>
+  </si>
+  <si>
+    <t>45,961,963.0</t>
+  </si>
+  <si>
+    <t>39,507,479.9</t>
+  </si>
+  <si>
+    <t>20,061,126.6</t>
+  </si>
+  <si>
+    <t>15,935,918.2</t>
+  </si>
+  <si>
+    <t>14,076,697.6</t>
+  </si>
+  <si>
+    <t>27,627,849.2</t>
+  </si>
+  <si>
+    <t>27,256,600.1</t>
+  </si>
+  <si>
+    <t>14,283,600.2</t>
+  </si>
+  <si>
+    <t>13,163,533.4</t>
+  </si>
+  <si>
+    <t>9,209,490.8</t>
+  </si>
+  <si>
+    <t>40,964,636.9</t>
+  </si>
+  <si>
+    <t>34,645,304.2</t>
+  </si>
+  <si>
+    <t>17,778,722.39</t>
+  </si>
+  <si>
+    <t>13,749,725.2</t>
+  </si>
+  <si>
+    <t>12,587,934.0</t>
+  </si>
+  <si>
+    <t>86,882,976.8</t>
+  </si>
+  <si>
+    <t>13,401,323.4</t>
+  </si>
+  <si>
+    <t>8,186,444.5</t>
+  </si>
+  <si>
+    <t>6,510,438.6</t>
+  </si>
+  <si>
+    <t>5,036,269.2</t>
+  </si>
+  <si>
+    <t>27,586,183.7</t>
+  </si>
+  <si>
+    <t>22,633,750.2</t>
+  </si>
+  <si>
+    <t>21,672,098.3</t>
+  </si>
+  <si>
+    <t>20,883,093.89</t>
+  </si>
+  <si>
+    <t>18,740,766.39</t>
+  </si>
+  <si>
+    <t>53,374,410.3</t>
+  </si>
+  <si>
+    <t>41,731,501.6</t>
+  </si>
+  <si>
+    <t>38,908,590.6</t>
+  </si>
+  <si>
+    <t>35,447,228.2</t>
+  </si>
+  <si>
+    <t>21,449,206.89</t>
+  </si>
+  <si>
+    <t>57,304,562.3</t>
+  </si>
+  <si>
+    <t>29,679,596.2</t>
+  </si>
+  <si>
+    <t>22,579,613.8</t>
+  </si>
+  <si>
+    <t>21,024,735.89</t>
+  </si>
+  <si>
+    <t>15,510,703.3</t>
+  </si>
+  <si>
+    <t>34,581,514.1</t>
+  </si>
+  <si>
+    <t>32,793,456.7</t>
+  </si>
+  <si>
+    <t>30,046,412.5</t>
+  </si>
+  <si>
+    <t>24,722,788.8</t>
+  </si>
+  <si>
+    <t>21,722,268.3</t>
+  </si>
+  <si>
+    <t>57,008,136.4</t>
+  </si>
+  <si>
+    <t>25,192,632.3</t>
+  </si>
+  <si>
+    <t>24,454,201.6</t>
+  </si>
+  <si>
+    <t>16,015,861.5</t>
+  </si>
+  <si>
+    <t>12,289,007.2</t>
+  </si>
+  <si>
+    <t>53,684,146.5</t>
+  </si>
+  <si>
+    <t>21,664,506.7</t>
+  </si>
+  <si>
+    <t>17,058,296.8</t>
+  </si>
+  <si>
+    <t>12,761,268.5</t>
+  </si>
+  <si>
+    <t>12,376,902.4</t>
+  </si>
+  <si>
+    <t>106,384,760.8</t>
+  </si>
+  <si>
+    <t>12,978,047.2</t>
+  </si>
+  <si>
+    <t>6,240,038.5</t>
+  </si>
+  <si>
+    <t>5,879,595.9</t>
+  </si>
+  <si>
+    <t>5,270,765.3</t>
+  </si>
+  <si>
+    <t>34,556,234.2</t>
+  </si>
+  <si>
+    <t>26,242,073.3</t>
+  </si>
+  <si>
+    <t>21,547,941.3</t>
+  </si>
+  <si>
+    <t>13,076,599.5</t>
+  </si>
+  <si>
+    <t>8,437,662.69</t>
   </si>
 </sst>
 </file>
@@ -1672,7 +1669,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.09337383172649925</v>
+        <v>0.1257607877186891</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1681,34 +1678,34 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.02173731499411417</v>
+        <v>0.03456000600835384</v>
       </c>
       <c r="H9" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>75</v>
-      </c>
       <c r="J9" s="14">
-        <v>0.07247433070632994</v>
+        <v>0.030165649445066</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>84</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.166936578262366</v>
+        <v>0.06052019551027914</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>93</v>
-      </c>
       <c r="P9" s="18">
-        <v>0.06513531325323937</v>
+        <v>0.04805358680773647</v>
       </c>
       <c r="Q9" s="15" t="s">
         <v>100</v>
@@ -1717,16 +1714,16 @@
         <v>101</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1401407389454402</v>
+        <v>0.1670341251505068</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V9" s="18">
-        <v>0.09908367545039258</v>
+        <v>0.035418492410083</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1738,7 +1735,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.05402041884046239</v>
+        <v>0.0469644618657477</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1747,34 +1744,34 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.01636319879917365</v>
+        <v>0.03286498151334249</v>
       </c>
       <c r="H10" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>77</v>
-      </c>
       <c r="J10" s="14">
-        <v>0.04633105540084562</v>
+        <v>0.02811705398737841</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="L10" s="15" t="s">
         <v>85</v>
       </c>
       <c r="M10" s="16">
-        <v>0.154763180793965</v>
+        <v>0.03030158181707551</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>95</v>
-      </c>
       <c r="P10" s="18">
-        <v>0.02542601359089278</v>
+        <v>0.02799454339462538</v>
       </c>
       <c r="Q10" s="15" t="s">
         <v>102</v>
@@ -1783,16 +1780,16 @@
         <v>103</v>
       </c>
       <c r="S10" s="16">
-        <v>0.08420336803406921</v>
+        <v>0.06114120782169731</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08013300265708966</v>
+        <v>0.02009083438459231</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1804,7 +1801,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.03586987102189999</v>
+        <v>0.01405889925869775</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1813,16 +1810,16 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.01318646111266273</v>
+        <v>0.02713087092325956</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="J11" s="14">
-        <v>0.02946421911796612</v>
+        <v>0.02094915594002849</v>
       </c>
       <c r="K11" s="15" t="s">
         <v>86</v>
@@ -1831,16 +1828,16 @@
         <v>87</v>
       </c>
       <c r="M11" s="16">
-        <v>0.1309353599452887</v>
+        <v>0.02437209867926764</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="O11" s="17" t="s">
         <v>96</v>
       </c>
       <c r="P11" s="18">
-        <v>0.02096387733196484</v>
+        <v>0.01890344813137678</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>104</v>
@@ -1849,16 +1846,16 @@
         <v>105</v>
       </c>
       <c r="S11" s="16">
-        <v>0.05286099266740186</v>
+        <v>0.05813361042587671</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05029977839741452</v>
+        <v>0.01952825910750752</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1870,7 +1867,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.0136699964948103</v>
+        <v>0.01314322231007584</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1879,25 +1876,25 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.0110396426540618</v>
+        <v>0.02000684120980823</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="I12" s="13" t="s">
         <v>80</v>
       </c>
       <c r="J12" s="14">
-        <v>0.02786348804748932</v>
+        <v>0.02052056553805887</v>
       </c>
       <c r="K12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="L12" s="15" t="s">
-        <v>89</v>
-      </c>
       <c r="M12" s="16">
-        <v>0.02471772826691269</v>
+        <v>0.01875628670351884</v>
       </c>
       <c r="N12" s="17" t="s">
         <v>97</v>
@@ -1906,25 +1903,25 @@
         <v>98</v>
       </c>
       <c r="P12" s="18">
-        <v>0.0209376354248927</v>
+        <v>0.01834943614188495</v>
       </c>
       <c r="Q12" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="R12" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="R12" s="15" t="s">
-        <v>107</v>
-      </c>
       <c r="S12" s="16">
-        <v>0.04906071689829452</v>
+        <v>0.01494478455482003</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="V12" s="18">
-        <v>0.02827158806204033</v>
+        <v>0.01930369751464274</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1936,7 +1933,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01125701759200133</v>
+        <v>0.01283757396705903</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>72</v>
@@ -1945,25 +1942,25 @@
         <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01055327987962486</v>
+        <v>0.01855977835960123</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="J13" s="14">
-        <v>0.02081246027176417</v>
+        <v>0.01354032921447386</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>91</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.01871261090359516</v>
+        <v>0.01549043720485259</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>54</v>
@@ -1972,25 +1969,25 @@
         <v>99</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01898080736443761</v>
+        <v>0.01511924015532539</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01708475053942412</v>
+        <v>0.006141179976404798</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02052996498384243</v>
+        <v>0.01912220935960395</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2001,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2010,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2019,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2028,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2037,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2046,7 +2043,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2055,7 +2052,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2064,133 +2061,133 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D16" s="10">
-        <v>0.05751117395481884</v>
+        <v>0.06034958932560699</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G16" s="12">
-        <v>0.3143051299749699</v>
+        <v>0.03797573844576117</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="J16" s="14">
-        <v>0.03565538451557851</v>
+        <v>0.02190082482734136</v>
       </c>
       <c r="K16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.1642204053293047</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.05050394785619527</v>
+      </c>
+      <c r="Q16" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.1096807254778088</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.04675076836882645</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>54</v>
-      </c>
       <c r="R16" s="15" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="S16" s="16">
-        <v>0.03231614133384639</v>
+        <v>0.2565826654210745</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="V16" s="18">
-        <v>0.1859537468790013</v>
+        <v>0.03871214813301303</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D17" s="10">
-        <v>0.05744198582632065</v>
+        <v>0.04908570484213341</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1141138313235565</v>
+        <v>0.01183376010597392</v>
       </c>
       <c r="H17" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="J17" s="14">
+        <v>0.02059712887218885</v>
+      </c>
+      <c r="K17" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="L17" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.04852804668959616</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="O17" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.03727716797834531</v>
+      </c>
+      <c r="Q17" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="J17" s="14">
-        <v>0.03405625212244063</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="L17" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="M17" s="16">
-        <v>0.02835297092042616</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="O17" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="P17" s="18">
-        <v>0.01892125680010422</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>86</v>
-      </c>
       <c r="R17" s="15" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="S17" s="16">
-        <v>0.02739840836339998</v>
+        <v>0.06903860593711814</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="V17" s="18">
-        <v>0.1697310089041129</v>
+        <v>0.02891709563611002</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2199,204 +2196,204 @@
         <v>56</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05348126267471428</v>
+        <v>0.04582545396914934</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>129</v>
-      </c>
       <c r="G18" s="12">
-        <v>0.06261332308832646</v>
+        <v>0.01167785439302441</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J18" s="14">
-        <v>0.01751911759360096</v>
+        <v>0.019380123575145</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M18" s="16">
-        <v>0.02228390210026311</v>
+        <v>0.01815473610274763</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="P18" s="18">
-        <v>0.01454951122030024</v>
+        <v>0.0272902349878542</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02645920486617647</v>
+        <v>0.02932681408861241</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="V18" s="18">
-        <v>0.02421059627670064</v>
+        <v>0.0197449495696456</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03212834598520144</v>
+        <v>0.03223162237168787</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>131</v>
-      </c>
       <c r="G19" s="12">
-        <v>0.01690013158085327</v>
+        <v>0.01089880154561151</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01642948426713055</v>
+        <v>0.01860119051606958</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>146</v>
+        <v>89</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01865562108890783</v>
+        <v>0.01693508011638799</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="P19" s="18">
-        <v>0.01443141332507071</v>
+        <v>0.02658783647016588</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02636627042624632</v>
+        <v>0.008856714919837761</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="V19" s="18">
-        <v>0.0221522592741689</v>
+        <v>0.0144779876720692</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D20" s="10">
-        <v>0.02722741122919919</v>
+        <v>0.01366742164002082</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G20" s="12">
-        <v>0.01096795809267892</v>
+        <v>0.01073632252443261</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J20" s="14">
-        <v>0.01446852239361847</v>
+        <v>0.01695114042850559</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01747999638858039</v>
+        <v>0.0167407030610397</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="O20" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.02411586986550736</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="P20" s="18">
-        <v>0.01276612392112208</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>164</v>
-      </c>
       <c r="R20" s="15" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02428230704697953</v>
+        <v>0.00762613818578764</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>116</v>
+        <v>167</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02052996498384243</v>
+        <v>0.01421178588666649</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2404,212 +2401,212 @@
         <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>109</v>
+        <v>175</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2218361163257</v>
+        <v>0.2425878199317637</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1536040384858389</v>
+        <v>0.1594826491136311</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1524549060709793</v>
+        <v>0.1230470174546781</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1264380145584153</v>
+        <v>0.1204899146989233</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D35" s="22">
-        <v>0.09296811269493699</v>
+        <v>0.1176795022460265</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D36" s="22">
-        <v>0.06558342994106495</v>
+        <v>0.09827236924544532</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04827332494711573</v>
+        <v>0.04777305586810032</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D38" s="22">
-        <v>0.0407404152099804</v>
+        <v>0.02729805474559835</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01969953871689244</v>
+        <v>0.01544373663802463</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01169014473623225</v>
+        <v>0.01410669070064895</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01083560577478618</v>
+        <v>0.01192559541215196</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D42" s="22">
-        <v>0.007630333296683879</v>
+        <v>0.007249981253485243</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D43" s="22">
-        <v>0.006942466505165295</v>
+        <v>0.007021575425401044</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001800020015860061</v>
+        <v>0.001992176578947096</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D45" s="22">
         <v>0.0001608180212491848</v>
@@ -2617,13 +2614,13 @@
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3002,331 +2999,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1024751021876125</v>
+        <v>0.1392524264113223</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G9" s="12">
-        <v>0.05721438647425212</v>
+        <v>0.1710948848521781</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1461469574964874</v>
+        <v>0.1331593117054012</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M9" s="16">
-        <v>0.1791581187455897</v>
+        <v>0.09171491276514417</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1345854335235337</v>
+        <v>0.139935454835576</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="S9" s="16">
-        <v>0.3201930970016988</v>
+        <v>0.3100252327450122</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1448472338648186</v>
+        <v>0.09946608252554905</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D10" s="10">
-        <v>0.09263001121925531</v>
+        <v>0.09507087864032228</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G10" s="12">
-        <v>0.05323519871675129</v>
+        <v>0.08156462623465854</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1421095065590155</v>
+        <v>0.1144596202450921</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="M10" s="16">
-        <v>0.16711906226317</v>
+        <v>0.09048249403525482</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P10" s="18">
-        <v>0.08941620319345521</v>
+        <v>0.1183485749667145</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="S10" s="16">
-        <v>0.0784930415734381</v>
+        <v>0.04782005128277532</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08855687681842332</v>
+        <v>0.0816093479887855</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D11" s="10">
-        <v>0.0768927655919132</v>
+        <v>0.08313505635172158</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G11" s="12">
-        <v>0.03237148805158997</v>
+        <v>0.0627030233399741</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J11" s="14">
-        <v>0.06347568432469484</v>
+        <v>0.05812035943919357</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M11" s="16">
-        <v>0.1572087358442032</v>
+        <v>0.04741661708198391</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P11" s="18">
-        <v>0.07593573948460544</v>
+        <v>0.06073222646920232</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="S11" s="16">
-        <v>0.07554523476907611</v>
+        <v>0.02921175649067569</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>112</v>
+        <v>244</v>
       </c>
       <c r="V11" s="18">
-        <v>0.05029977839741452</v>
+        <v>0.0781419692354768</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D12" s="10">
-        <v>0.06913574622384616</v>
+        <v>0.05649637188172188</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G12" s="12">
-        <v>0.03169285614772131</v>
+        <v>0.05384478419681581</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J12" s="14">
-        <v>0.05664372923240111</v>
+        <v>0.04616895712016425</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04371194076478214</v>
+        <v>0.04369838233596778</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="P12" s="18">
-        <v>0.05746493907283241</v>
+        <v>0.0469691469357606</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="S12" s="16">
-        <v>0.04968797510546561</v>
+        <v>0.02323125100655058</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="V12" s="18">
-        <v>0.04199545309088224</v>
+        <v>0.07529709668562055</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D13" s="10">
-        <v>0.05719443531774115</v>
+        <v>0.05081971977392151</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G13" s="12">
-        <v>0.02868227697515132</v>
+        <v>0.04342110262873179</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J13" s="14">
-        <v>0.05247454099526935</v>
+        <v>0.0407824914593198</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="M13" s="16">
-        <v>0.02230471997305282</v>
+        <v>0.03057232719126749</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P13" s="18">
-        <v>0.04286210321766017</v>
+        <v>0.0430004609592966</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02630903820412303</v>
+        <v>0.01797096034693572</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="V13" s="18">
-        <v>0.02404686168407763</v>
+        <v>0.0675726166984974</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3337,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3346,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3355,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3364,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3373,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3382,7 +3379,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3391,7 +3388,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3400,331 +3397,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1044212825041796</v>
+        <v>0.1115409444359699</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G16" s="12">
-        <v>0.3246731097769735</v>
+        <v>0.1515329274068925</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1023487842008392</v>
+        <v>0.1001882929866731</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1702759886313545</v>
+        <v>0.1892473141495734</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P16" s="18">
-        <v>0.1525301415886741</v>
+        <v>0.1833853788641098</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1229835063018404</v>
+        <v>0.3796136072025383</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="V16" s="18">
-        <v>0.2491686803944716</v>
+        <v>0.124597634819252</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D17" s="10">
-        <v>0.1032035603724327</v>
+        <v>0.08720978976689867</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G17" s="12">
-        <v>0.1242242873637122</v>
+        <v>0.07848303723001274</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J17" s="14">
-        <v>0.09600627166029851</v>
+        <v>0.0950079987361044</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M17" s="16">
-        <v>0.07035567253604655</v>
+        <v>0.08363083412656144</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="P17" s="18">
-        <v>0.08590236337411075</v>
+        <v>0.07400608984411339</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="S17" s="16">
-        <v>0.07235212618679972</v>
+        <v>0.04630967137575969</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="V17" s="18">
-        <v>0.2156327130701514</v>
+        <v>0.09461969284643412</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D18" s="10">
-        <v>0.1018254240004877</v>
+        <v>0.08131051786433512</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G18" s="12">
-        <v>0.07358128118100538</v>
+        <v>0.05970824732799799</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J18" s="14">
-        <v>0.08555666452835389</v>
+        <v>0.08704936313787474</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="M18" s="16">
-        <v>0.03097220909878528</v>
+        <v>0.08117949936129118</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05647323791831867</v>
+        <v>0.05827124813178192</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04263861511442749</v>
+        <v>0.02226638013052445</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="V18" s="18">
-        <v>0.03105281521132287</v>
+        <v>0.07769430273175071</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D19" s="10">
-        <v>0.08697576376740529</v>
+        <v>0.07407702097020352</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G19" s="12">
-        <v>0.04472568944071944</v>
+        <v>0.05559661658708433</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="J19" s="14">
-        <v>0.06212931060266153</v>
+        <v>0.07162595601162643</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="M19" s="16">
-        <v>0.02369364887472276</v>
+        <v>0.05316712602916375</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="P19" s="18">
-        <v>0.04899141214903799</v>
+        <v>0.04359257269106682</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03567114154237874</v>
+        <v>0.02098020986942196</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02749422865955769</v>
+        <v>0.04714962167893319</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D20" s="10">
-        <v>0.04226140145253712</v>
+        <v>0.04482419162256342</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G20" s="12">
-        <v>0.03883996586637172</v>
+        <v>0.0410156221922447</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J20" s="14">
-        <v>0.05622683040712356</v>
+        <v>0.0629329581834452</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01711192064769691</v>
+        <v>0.04079525753739196</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P20" s="18">
-        <v>0.04645705560415778</v>
+        <v>0.04227957569909601</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="S20" s="16">
-        <v>0.02314380705911725</v>
+        <v>0.01880771468775036</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>169</v>
+        <v>281</v>
       </c>
       <c r="V20" s="18">
-        <v>0.02421059627670064</v>
+        <v>0.03042324605563135</v>
       </c>
     </row>
   </sheetData>

--- a/Daily_Report/Top 7 broker List with its Turnover 2024-07-08.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-07-08.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="280">
   <si>
     <t>Date: 2024-07-08</t>
   </si>
@@ -68,12 +68,12 @@
     <t>Imperial Securities Co .Pvt.Limited</t>
   </si>
   <si>
+    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
-  </si>
-  <si>
     <t>Linch Stock Market Limited</t>
   </si>
   <si>
@@ -89,79 +89,79 @@
     <t>45</t>
   </si>
   <si>
+    <t>44</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
     <t>41</t>
   </si>
   <si>
     <t>42</t>
   </si>
   <si>
-    <t>478,518,543.75</t>
-  </si>
-  <si>
-    <t>378,165,744.44</t>
-  </si>
-  <si>
-    <t>345,165,219.1</t>
-  </si>
-  <si>
-    <t>301,236,171.6</t>
-  </si>
-  <si>
-    <t>292,739,513.0</t>
-  </si>
-  <si>
-    <t>280,244,856.3</t>
-  </si>
-  <si>
-    <t>277,342,617.7</t>
-  </si>
-  <si>
-    <t>239,330,868.05</t>
-  </si>
-  <si>
-    <t>206,088,191.7</t>
-  </si>
-  <si>
-    <t>168,828,670.69</t>
-  </si>
-  <si>
-    <t>130,591,766.1</t>
-  </si>
-  <si>
-    <t>147,266,748.1</t>
-  </si>
-  <si>
-    <t>130,229,965.3</t>
-  </si>
-  <si>
-    <t>148,012,149.6</t>
-  </si>
-  <si>
-    <t>239,187,675.7</t>
-  </si>
-  <si>
-    <t>172,077,552.74</t>
-  </si>
-  <si>
-    <t>176,336,548.4</t>
-  </si>
-  <si>
-    <t>170,644,405.5</t>
-  </si>
-  <si>
-    <t>145,472,764.9</t>
-  </si>
-  <si>
-    <t>150,014,891.0</t>
-  </si>
-  <si>
-    <t>129,330,468.1</t>
+    <t>610,282,898.21</t>
+  </si>
+  <si>
+    <t>375,008,018.44</t>
+  </si>
+  <si>
+    <t>339,405,313.1</t>
+  </si>
+  <si>
+    <t>311,349,115.7</t>
+  </si>
+  <si>
+    <t>303,348,643.6</t>
+  </si>
+  <si>
+    <t>285,874,105.8</t>
+  </si>
+  <si>
+    <t>259,277,592.1</t>
+  </si>
+  <si>
+    <t>305,527,695.51</t>
+  </si>
+  <si>
+    <t>202,571,416.0</t>
+  </si>
+  <si>
+    <t>176,075,017.2</t>
+  </si>
+  <si>
+    <t>165,391,012.6</t>
+  </si>
+  <si>
+    <t>131,964,367.1</t>
+  </si>
+  <si>
+    <t>130,823,673.5</t>
+  </si>
+  <si>
+    <t>142,844,288.8</t>
+  </si>
+  <si>
+    <t>304,755,202.7</t>
+  </si>
+  <si>
+    <t>172,436,602.44</t>
+  </si>
+  <si>
+    <t>163,330,295.9</t>
+  </si>
+  <si>
+    <t>145,958,103.1</t>
+  </si>
+  <si>
+    <t>171,384,276.5</t>
+  </si>
+  <si>
+    <t>155,050,432.3</t>
+  </si>
+  <si>
+    <t>116,433,303.3</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -182,7 +182,7 @@
     <t>NRN</t>
   </si>
   <si>
-    <t>60,178,869.0</t>
+    <t>118,415,351.7</t>
   </si>
   <si>
     <t>FOWAD</t>
@@ -194,448 +194,442 @@
     <t>SAMAJ</t>
   </si>
   <si>
-    <t>6,727,444.0</t>
+    <t>8,607,648.0</t>
   </si>
   <si>
     <t>MKHL</t>
   </si>
   <si>
-    <t>6,289,275.6</t>
-  </si>
-  <si>
-    <t>LBBL</t>
-  </si>
-  <si>
-    <t>6,143,017.2</t>
-  </si>
-  <si>
-    <t>SBI</t>
-  </si>
-  <si>
-    <t>13,069,410.4</t>
+    <t>7,713,268.6</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>6,527,525.1</t>
+  </si>
+  <si>
+    <t>ALICL</t>
+  </si>
+  <si>
+    <t>12,888,244.0</t>
+  </si>
+  <si>
+    <t>MFIL</t>
+  </si>
+  <si>
+    <t>9,738,182.4</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>7,690,177.0</t>
+  </si>
+  <si>
+    <t>7,472,358.3</t>
   </si>
   <si>
     <t>NRM</t>
   </si>
   <si>
-    <t>12,428,410.2</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>10,259,966.0</t>
-  </si>
-  <si>
-    <t>MKCL</t>
-  </si>
-  <si>
-    <t>7,565,902.0</t>
-  </si>
-  <si>
-    <t>MFIL</t>
-  </si>
-  <si>
-    <t>7,018,672.4</t>
+    <t>7,421,148.2</t>
   </si>
   <si>
     <t>10,412,133.0</t>
   </si>
   <si>
+    <t>RLFL</t>
+  </si>
+  <si>
+    <t>7,230,920.0</t>
+  </si>
+  <si>
+    <t>SFCL</t>
+  </si>
+  <si>
+    <t>7,082,985.5</t>
+  </si>
+  <si>
     <t>ICFC</t>
   </si>
   <si>
-    <t>9,705,029.1</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>7,230,920.0</t>
-  </si>
-  <si>
-    <t>SFCL</t>
-  </si>
-  <si>
-    <t>7,082,985.5</t>
-  </si>
-  <si>
-    <t>4,673,650.7</t>
+    <t>6,112,425.1</t>
+  </si>
+  <si>
+    <t>3,918,694.0</t>
+  </si>
+  <si>
+    <t>MSLB</t>
+  </si>
+  <si>
+    <t>14,067,183.6</t>
+  </si>
+  <si>
+    <t>SPIL</t>
+  </si>
+  <si>
+    <t>8,195,109.0</t>
+  </si>
+  <si>
+    <t>ACLBSL</t>
+  </si>
+  <si>
+    <t>6,924,457.8</t>
+  </si>
+  <si>
+    <t>SMJC</t>
+  </si>
+  <si>
+    <t>6,540,900.0</t>
+  </si>
+  <si>
+    <t>5,905,999.0</t>
+  </si>
+  <si>
+    <t>OHL</t>
+  </si>
+  <si>
+    <t>8,353,212.5</t>
+  </si>
+  <si>
+    <t>NLIC</t>
+  </si>
+  <si>
+    <t>7,430,957.7</t>
   </si>
   <si>
     <t>HEI</t>
   </si>
   <si>
-    <t>18,230,872.0</t>
-  </si>
-  <si>
-    <t>OHL</t>
-  </si>
-  <si>
-    <t>9,127,932.5</t>
-  </si>
-  <si>
-    <t>NLIC</t>
-  </si>
-  <si>
-    <t>7,341,757.7</t>
-  </si>
-  <si>
-    <t>5,650,072.0</t>
+    <t>6,621,417.0</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>6,482,111.6</t>
+  </si>
+  <si>
+    <t>6,218,516.1</t>
+  </si>
+  <si>
+    <t>42,563,438.4</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>17,598,845.3</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>16,356,995.3</t>
+  </si>
+  <si>
+    <t>5,755,407.8</t>
+  </si>
+  <si>
+    <t>1,840,034.1</t>
+  </si>
+  <si>
+    <t>7,027,451.8</t>
+  </si>
+  <si>
+    <t>SWMF</t>
+  </si>
+  <si>
+    <t>6,914,081.8</t>
+  </si>
+  <si>
+    <t>SADBL</t>
+  </si>
+  <si>
+    <t>5,572,044.6</t>
+  </si>
+  <si>
+    <t>5,540,018.5</t>
+  </si>
+  <si>
+    <t>MLBL</t>
+  </si>
+  <si>
+    <t>5,273,139.4</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>75,356,219.9</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>23,488,420.0</t>
+  </si>
+  <si>
+    <t>21,928,329.5</t>
+  </si>
+  <si>
+    <t>16,238,972.0</t>
+  </si>
+  <si>
+    <t>NTC</t>
+  </si>
+  <si>
+    <t>6,540,114.7</t>
+  </si>
+  <si>
+    <t>HRL</t>
+  </si>
+  <si>
+    <t>14,480,317.4</t>
+  </si>
+  <si>
+    <t>4,727,874.5</t>
+  </si>
+  <si>
+    <t>4,543,723.9</t>
+  </si>
+  <si>
+    <t>ILBS</t>
+  </si>
+  <si>
+    <t>4,511,122.7</t>
+  </si>
+  <si>
+    <t>RHPL</t>
+  </si>
+  <si>
+    <t>4,416,164.5</t>
+  </si>
+  <si>
+    <t>6,420,484.0</t>
+  </si>
+  <si>
+    <t>6,157,494.1</t>
+  </si>
+  <si>
+    <t>5,965,650.2</t>
+  </si>
+  <si>
+    <t>EDBL</t>
+  </si>
+  <si>
+    <t>5,940,500.1</t>
+  </si>
+  <si>
+    <t>4,874,885.2</t>
+  </si>
+  <si>
+    <t>14,866,201.1</t>
+  </si>
+  <si>
+    <t>SWBBL</t>
+  </si>
+  <si>
+    <t>13,350,441.5</t>
+  </si>
+  <si>
+    <t>GBIME</t>
+  </si>
+  <si>
+    <t>7,988,930.1</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>7,059,668.0</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>5,494,528.6</t>
+  </si>
+  <si>
+    <t>43,873,305.2</t>
+  </si>
+  <si>
+    <t>CLI</t>
+  </si>
+  <si>
+    <t>9,837,089.19</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>6,426,283.5</t>
+  </si>
+  <si>
+    <t>5,310,410.1</t>
   </si>
   <si>
     <t>NLG</t>
   </si>
   <si>
-    <t>4,666,280.0</t>
-  </si>
-  <si>
-    <t>MSLB</t>
-  </si>
-  <si>
-    <t>14,067,183.6</t>
-  </si>
-  <si>
-    <t>SPIL</t>
-  </si>
-  <si>
-    <t>8,195,109.0</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>5,533,786.2</t>
-  </si>
-  <si>
-    <t>SMJC</t>
-  </si>
-  <si>
-    <t>5,371,605.0</t>
-  </si>
-  <si>
-    <t>4,425,999.0</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>46,810,454.4</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>17,134,509.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>16,291,645.3</t>
-  </si>
-  <si>
-    <t>4,188,199.0</t>
-  </si>
-  <si>
-    <t>1,721,034.1</t>
-  </si>
-  <si>
-    <t>9,823,057.4</t>
-  </si>
-  <si>
-    <t>SADBL</t>
-  </si>
-  <si>
-    <t>5,572,044.6</t>
-  </si>
-  <si>
-    <t>5,416,018.5</t>
-  </si>
-  <si>
-    <t>5,353,738.0</t>
-  </si>
-  <si>
-    <t>VLBS</t>
-  </si>
-  <si>
-    <t>5,303,403.59</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>28,878,397.6</t>
-  </si>
-  <si>
-    <t>MEN</t>
-  </si>
-  <si>
-    <t>23,488,420.0</t>
-  </si>
-  <si>
-    <t>21,928,329.5</t>
-  </si>
-  <si>
-    <t>15,423,429.0</t>
-  </si>
-  <si>
-    <t>NTC</t>
-  </si>
-  <si>
-    <t>6,540,114.7</t>
-  </si>
-  <si>
-    <t>HRL</t>
-  </si>
-  <si>
-    <t>14,361,123.4</t>
-  </si>
-  <si>
-    <t>ILBS</t>
-  </si>
-  <si>
-    <t>4,475,122.7</t>
-  </si>
-  <si>
-    <t>RHPL</t>
-  </si>
-  <si>
-    <t>4,416,164.5</t>
-  </si>
-  <si>
-    <t>RNLI</t>
-  </si>
-  <si>
-    <t>4,121,553.4</t>
-  </si>
-  <si>
-    <t>4,060,109.4</t>
-  </si>
-  <si>
-    <t>7,559,403.0</t>
+    <t>5,101,458.7</t>
+  </si>
+  <si>
+    <t>74,287,500.0</t>
+  </si>
+  <si>
+    <t>19,278,145.6</t>
+  </si>
+  <si>
+    <t>8,164,804.8</t>
+  </si>
+  <si>
+    <t>2,488,358.79</t>
+  </si>
+  <si>
+    <t>2,183,069.2</t>
+  </si>
+  <si>
+    <t>NGPL</t>
+  </si>
+  <si>
+    <t>11,724,495.0</t>
+  </si>
+  <si>
+    <t>3,941,533.9</t>
+  </si>
+  <si>
+    <t>CITY</t>
+  </si>
+  <si>
+    <t>3,182,663.0</t>
+  </si>
+  <si>
+    <t>2,987,181.4</t>
+  </si>
+  <si>
+    <t>GMFIL</t>
+  </si>
+  <si>
+    <t>2,695,600.0</t>
+  </si>
+  <si>
+    <t>Top Traded Stocks</t>
+  </si>
+  <si>
+    <t>Turnover (Rs.)</t>
+  </si>
+  <si>
+    <t>Sub Indices</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Percentage (%)</t>
+  </si>
+  <si>
+    <t>287,080,935.8</t>
+  </si>
+  <si>
+    <t>155,551,282.19</t>
+  </si>
+  <si>
+    <t>96,392,418.7</t>
+  </si>
+  <si>
+    <t>90,418,318.3</t>
   </si>
   <si>
     <t>NIFRA</t>
   </si>
   <si>
-    <t>7,109,412.5</t>
-  </si>
-  <si>
-    <t>SNLI</t>
-  </si>
-  <si>
-    <t>6,689,344.6</t>
-  </si>
-  <si>
-    <t>6,420,484.0</t>
-  </si>
-  <si>
-    <t>5,850,944.1</t>
-  </si>
-  <si>
-    <t>49,469,126.2</t>
-  </si>
-  <si>
-    <t>14,618,403.0</t>
-  </si>
-  <si>
-    <t>CLI</t>
-  </si>
-  <si>
-    <t>5,468,863.2</t>
-  </si>
-  <si>
-    <t>5,101,458.7</t>
-  </si>
-  <si>
-    <t>NRIC</t>
-  </si>
-  <si>
-    <t>5,042,905.3</t>
-  </si>
-  <si>
-    <t>14,784,501.1</t>
-  </si>
-  <si>
-    <t>SINDU</t>
-  </si>
-  <si>
-    <t>10,912,500.0</t>
-  </si>
-  <si>
-    <t>GBIME</t>
-  </si>
-  <si>
-    <t>7,988,930.1</t>
-  </si>
-  <si>
-    <t>7,783,310.3</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>7,059,668.0</t>
-  </si>
-  <si>
-    <t>71,905,972.2</t>
-  </si>
-  <si>
-    <t>19,347,714.2</t>
-  </si>
-  <si>
-    <t>8,218,688.8</t>
-  </si>
-  <si>
-    <t>2,482,048.79</t>
-  </si>
-  <si>
-    <t>ENL</t>
-  </si>
-  <si>
-    <t>2,137,186.0</t>
-  </si>
-  <si>
-    <t>10,736,528.5</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>8,019,943.0</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>5,476,116.0</t>
-  </si>
-  <si>
-    <t>CITY</t>
-  </si>
-  <si>
-    <t>4,015,363.0</t>
-  </si>
-  <si>
-    <t>3,941,533.9</t>
-  </si>
-  <si>
-    <t>Top Traded Stocks</t>
-  </si>
-  <si>
-    <t>Turnover (Rs.)</t>
-  </si>
-  <si>
-    <t>Sub Indices</t>
-  </si>
-  <si>
-    <t>Turnover</t>
-  </si>
-  <si>
-    <t>Percentage (%)</t>
-  </si>
-  <si>
-    <t>315,936,900.1</t>
-  </si>
-  <si>
-    <t>152,019,809.8</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>89,626,344.2</t>
-  </si>
-  <si>
-    <t>82,276,993.2</t>
-  </si>
-  <si>
-    <t>81,494,384.3</t>
+    <t>73,572,657.59</t>
   </si>
   <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>1,108,586,578.4</t>
+    <t>1,098,402,257.7</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>728,809,568.2</t>
+    <t>721,262,604.38</t>
+  </si>
+  <si>
+    <t>Microfinance</t>
+  </si>
+  <si>
+    <t>590,668,334.0</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>562,304,703.1</t>
-  </si>
-  <si>
-    <t>Microfinance</t>
-  </si>
-  <si>
-    <t>550,619,162.6</t>
+    <t>583,597,726.76</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>537,776,038.29</t>
+    <t>514,853,282.1</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>449,088,621.2</t>
+    <t>441,414,821.9</t>
   </si>
   <si>
     <t>Commercial Banks</t>
   </si>
   <si>
-    <t>218,315,035.6</t>
+    <t>210,156,466.1</t>
   </si>
   <si>
     <t>Non Life Insurance</t>
   </si>
   <si>
-    <t>124,747,636.2</t>
+    <t>116,764,908.6</t>
   </si>
   <si>
     <t>Manufacturing And Processing</t>
   </si>
   <si>
-    <t>70,575,345.3</t>
+    <t>73,200,030.7</t>
   </si>
   <si>
     <t>Life Insurance</t>
   </si>
   <si>
-    <t>64,465,264.5</t>
+    <t>72,206,609.09</t>
   </si>
   <si>
     <t>Hotels And Tourism</t>
   </si>
   <si>
-    <t>54,498,016.5</t>
+    <t>59,596,604.0</t>
   </si>
   <si>
     <t>Trading</t>
   </si>
   <si>
-    <t>33,131,226.1</t>
+    <t>39,214,286.1</t>
   </si>
   <si>
     <t>Others</t>
   </si>
   <si>
-    <t>32,087,448.9</t>
+    <t>38,455,306.1</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>9,103,920.46</t>
+    <t>9,307,956.46</t>
   </si>
   <si>
     <t>Tradings</t>
@@ -653,214 +647,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>66,634,868.3</t>
-  </si>
-  <si>
-    <t>45,493,178.4</t>
-  </si>
-  <si>
-    <t>39,781,666.1</t>
-  </si>
-  <si>
-    <t>27,034,561.6</t>
-  </si>
-  <si>
-    <t>24,318,178.3</t>
-  </si>
-  <si>
-    <t>64,702,224.5</t>
-  </si>
-  <si>
-    <t>30,844,947.6</t>
-  </si>
-  <si>
-    <t>23,712,135.5</t>
-  </si>
-  <si>
-    <t>20,362,252.89</t>
-  </si>
-  <si>
-    <t>16,420,373.6</t>
-  </si>
-  <si>
-    <t>45,961,963.0</t>
-  </si>
-  <si>
-    <t>39,507,479.9</t>
-  </si>
-  <si>
-    <t>20,061,126.6</t>
-  </si>
-  <si>
-    <t>15,935,918.2</t>
-  </si>
-  <si>
-    <t>14,076,697.6</t>
-  </si>
-  <si>
-    <t>27,627,849.2</t>
-  </si>
-  <si>
-    <t>27,256,600.1</t>
-  </si>
-  <si>
-    <t>14,283,600.2</t>
-  </si>
-  <si>
-    <t>13,163,533.4</t>
-  </si>
-  <si>
-    <t>9,209,490.8</t>
-  </si>
-  <si>
-    <t>40,964,636.9</t>
-  </si>
-  <si>
-    <t>34,645,304.2</t>
-  </si>
-  <si>
-    <t>17,778,722.39</t>
-  </si>
-  <si>
-    <t>13,749,725.2</t>
-  </si>
-  <si>
-    <t>12,587,934.0</t>
-  </si>
-  <si>
-    <t>86,882,976.8</t>
-  </si>
-  <si>
-    <t>13,401,323.4</t>
-  </si>
-  <si>
-    <t>8,186,444.5</t>
-  </si>
-  <si>
-    <t>6,510,438.6</t>
-  </si>
-  <si>
-    <t>5,036,269.2</t>
-  </si>
-  <si>
-    <t>27,586,183.7</t>
-  </si>
-  <si>
-    <t>22,633,750.2</t>
-  </si>
-  <si>
-    <t>21,672,098.3</t>
-  </si>
-  <si>
-    <t>20,883,093.89</t>
-  </si>
-  <si>
-    <t>18,740,766.39</t>
-  </si>
-  <si>
-    <t>53,374,410.3</t>
-  </si>
-  <si>
-    <t>41,731,501.6</t>
-  </si>
-  <si>
-    <t>38,908,590.6</t>
-  </si>
-  <si>
-    <t>35,447,228.2</t>
-  </si>
-  <si>
-    <t>21,449,206.89</t>
-  </si>
-  <si>
-    <t>57,304,562.3</t>
-  </si>
-  <si>
-    <t>29,679,596.2</t>
-  </si>
-  <si>
-    <t>22,579,613.8</t>
-  </si>
-  <si>
-    <t>21,024,735.89</t>
-  </si>
-  <si>
-    <t>15,510,703.3</t>
-  </si>
-  <si>
-    <t>34,581,514.1</t>
-  </si>
-  <si>
-    <t>32,793,456.7</t>
-  </si>
-  <si>
-    <t>30,046,412.5</t>
-  </si>
-  <si>
-    <t>24,722,788.8</t>
-  </si>
-  <si>
-    <t>21,722,268.3</t>
-  </si>
-  <si>
-    <t>57,008,136.4</t>
-  </si>
-  <si>
-    <t>25,192,632.3</t>
-  </si>
-  <si>
-    <t>24,454,201.6</t>
-  </si>
-  <si>
-    <t>16,015,861.5</t>
-  </si>
-  <si>
-    <t>12,289,007.2</t>
-  </si>
-  <si>
-    <t>53,684,146.5</t>
-  </si>
-  <si>
-    <t>21,664,506.7</t>
-  </si>
-  <si>
-    <t>17,058,296.8</t>
-  </si>
-  <si>
-    <t>12,761,268.5</t>
-  </si>
-  <si>
-    <t>12,376,902.4</t>
-  </si>
-  <si>
-    <t>106,384,760.8</t>
-  </si>
-  <si>
-    <t>12,978,047.2</t>
-  </si>
-  <si>
-    <t>6,240,038.5</t>
-  </si>
-  <si>
-    <t>5,879,595.9</t>
-  </si>
-  <si>
-    <t>5,270,765.3</t>
-  </si>
-  <si>
-    <t>34,556,234.2</t>
-  </si>
-  <si>
-    <t>26,242,073.3</t>
-  </si>
-  <si>
-    <t>21,547,941.3</t>
-  </si>
-  <si>
-    <t>13,076,599.5</t>
-  </si>
-  <si>
-    <t>8,437,662.69</t>
+    <t>126,108,834.0</t>
+  </si>
+  <si>
+    <t>50,562,855.4</t>
+  </si>
+  <si>
+    <t>39,602,725.1</t>
+  </si>
+  <si>
+    <t>26,330,424.4</t>
+  </si>
+  <si>
+    <t>25,769,084.86</t>
+  </si>
+  <si>
+    <t>54,488,285.0</t>
+  </si>
+  <si>
+    <t>35,211,741.1</t>
+  </si>
+  <si>
+    <t>23,531,009.5</t>
+  </si>
+  <si>
+    <t>22,069,466.9</t>
+  </si>
+  <si>
+    <t>16,155,660.1</t>
+  </si>
+  <si>
+    <t>44,002,397.0</t>
+  </si>
+  <si>
+    <t>42,432,110.9</t>
+  </si>
+  <si>
+    <t>21,015,628.39</t>
+  </si>
+  <si>
+    <t>16,677,271.2</t>
+  </si>
+  <si>
+    <t>15,374,708.9</t>
+  </si>
+  <si>
+    <t>45,725,467.7</t>
+  </si>
+  <si>
+    <t>38,412,166.7</t>
+  </si>
+  <si>
+    <t>18,440,623.39</t>
+  </si>
+  <si>
+    <t>14,372,099.6</t>
+  </si>
+  <si>
+    <t>13,910,473.2</t>
+  </si>
+  <si>
+    <t>37,464,456.0</t>
+  </si>
+  <si>
+    <t>15,647,145.1</t>
+  </si>
+  <si>
+    <t>13,711,717.2</t>
+  </si>
+  <si>
+    <t>13,387,755.8</t>
+  </si>
+  <si>
+    <t>8,915,576.3</t>
+  </si>
+  <si>
+    <t>83,296,456.09</t>
+  </si>
+  <si>
+    <t>13,434,484.9</t>
+  </si>
+  <si>
+    <t>8,855,703.9</t>
+  </si>
+  <si>
+    <t>8,290,423.6</t>
+  </si>
+  <si>
+    <t>5,835,499.2</t>
+  </si>
+  <si>
+    <t>31,382,705.5</t>
+  </si>
+  <si>
+    <t>23,501,656.7</t>
+  </si>
+  <si>
+    <t>21,887,825.1</t>
+  </si>
+  <si>
+    <t>21,607,320.8</t>
+  </si>
+  <si>
+    <t>16,667,696.6</t>
+  </si>
+  <si>
+    <t>83,497,761.9</t>
+  </si>
+  <si>
+    <t>59,833,320.6</t>
+  </si>
+  <si>
+    <t>46,741,589.2</t>
+  </si>
+  <si>
+    <t>40,635,777.19</t>
+  </si>
+  <si>
+    <t>23,043,098.5</t>
+  </si>
+  <si>
+    <t>55,121,983.5</t>
+  </si>
+  <si>
+    <t>30,347,613.2</t>
+  </si>
+  <si>
+    <t>22,787,020.8</t>
+  </si>
+  <si>
+    <t>19,272,717.89</t>
+  </si>
+  <si>
+    <t>16,522,366.3</t>
+  </si>
+  <si>
+    <t>30,226,729.5</t>
+  </si>
+  <si>
+    <t>29,899,391.2</t>
+  </si>
+  <si>
+    <t>26,855,216.7</t>
+  </si>
+  <si>
+    <t>25,405,530.8</t>
+  </si>
+  <si>
+    <t>20,531,503.3</t>
+  </si>
+  <si>
+    <t>57,639,214.1</t>
+  </si>
+  <si>
+    <t>28,052,554.2</t>
+  </si>
+  <si>
+    <t>12,976,624.9</t>
+  </si>
+  <si>
+    <t>12,634,902.5</t>
+  </si>
+  <si>
+    <t>8,606,799.9</t>
+  </si>
+  <si>
+    <t>53,885,649.7</t>
+  </si>
+  <si>
+    <t>32,543,932.3</t>
+  </si>
+  <si>
+    <t>17,054,346.5</t>
+  </si>
+  <si>
+    <t>14,662,948.6</t>
+  </si>
+  <si>
+    <t>13,562,558.2</t>
+  </si>
+  <si>
+    <t>108,670,592.0</t>
+  </si>
+  <si>
+    <t>13,573,673.0</t>
+  </si>
+  <si>
+    <t>6,409,149.6</t>
+  </si>
+  <si>
+    <t>6,206,633.2</t>
+  </si>
+  <si>
+    <t>5,916,953.7</t>
+  </si>
+  <si>
+    <t>26,498,646.3</t>
+  </si>
+  <si>
+    <t>24,465,247.2</t>
+  </si>
+  <si>
+    <t>17,345,876.6</t>
+  </si>
+  <si>
+    <t>12,368,582.9</t>
+  </si>
+  <si>
+    <t>8,487,485.8</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +1663,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1257607877186891</v>
+        <v>0.1940335409157295</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1678,52 +1672,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.03456000600835384</v>
+        <v>0.03436791579447807</v>
       </c>
       <c r="H9" s="13" t="s">
         <v>54</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J9" s="14">
-        <v>0.030165649445066</v>
+        <v>0.03067757809946906</v>
       </c>
       <c r="K9" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="L9" s="15" t="s">
-        <v>83</v>
-      </c>
       <c r="M9" s="16">
-        <v>0.06052019551027914</v>
+        <v>0.04518138286139992</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>92</v>
-      </c>
       <c r="P9" s="18">
-        <v>0.04805358680773647</v>
+        <v>0.02753667331710462</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1670341251505068</v>
+        <v>0.1488887504549914</v>
       </c>
       <c r="T9" s="17" t="s">
         <v>54</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="V9" s="18">
-        <v>0.035418492410083</v>
+        <v>0.02710396892798049</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1735,7 +1729,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.0469644618657477</v>
+        <v>0.03682450543168728</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1744,52 +1738,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.03286498151334249</v>
+        <v>0.02596793114053927</v>
       </c>
       <c r="H10" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>76</v>
-      </c>
       <c r="J10" s="14">
-        <v>0.02811705398737841</v>
+        <v>0.02130467532742934</v>
       </c>
       <c r="K10" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="15" t="s">
-        <v>85</v>
-      </c>
       <c r="M10" s="16">
-        <v>0.03030158181707551</v>
+        <v>0.02632128561398063</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>94</v>
-      </c>
       <c r="P10" s="18">
-        <v>0.02799454339462538</v>
+        <v>0.02449642632916655</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S10" s="16">
-        <v>0.06114120782169731</v>
+        <v>0.06156152286248796</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V10" s="18">
-        <v>0.02009083438459231</v>
+        <v>0.02666671556149491</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1801,7 +1795,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.01405889925869775</v>
+        <v>0.01410435721736067</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1810,52 +1804,52 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.02713087092325956</v>
+        <v>0.02050670018201331</v>
       </c>
       <c r="H11" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>78</v>
-      </c>
       <c r="J11" s="14">
-        <v>0.02094915594002849</v>
+        <v>0.02086881149651632</v>
       </c>
       <c r="K11" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L11" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="L11" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="M11" s="16">
-        <v>0.02437209867926764</v>
+        <v>0.02224017172630113</v>
       </c>
       <c r="N11" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="O11" s="17" t="s">
-        <v>96</v>
-      </c>
       <c r="P11" s="18">
-        <v>0.01890344813137678</v>
+        <v>0.02182774553207199</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S11" s="16">
-        <v>0.05813361042587671</v>
+        <v>0.05721747779228209</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01952825910750752</v>
+        <v>0.02149065237327156</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1867,61 +1861,61 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01314322231007584</v>
+        <v>0.01263884113846795</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
       <c r="G12" s="12">
-        <v>0.02000684120980823</v>
+        <v>0.01992586273510723</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="J12" s="14">
-        <v>0.02052056553805887</v>
+        <v>0.01800922043373869</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="L12" s="15" t="s">
         <v>88</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01875628670351884</v>
+        <v>0.02100824980759693</v>
       </c>
       <c r="N12" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="O12" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>98</v>
-      </c>
       <c r="P12" s="18">
-        <v>0.01834943614188495</v>
+        <v>0.02136852013931339</v>
       </c>
       <c r="Q12" s="15" t="s">
         <v>54</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S12" s="16">
-        <v>0.01494478455482003</v>
+        <v>0.02013266568475612</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="V12" s="18">
-        <v>0.01930369751464274</v>
+        <v>0.02136713186484425</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1933,61 +1927,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01283757396705903</v>
+        <v>0.01069590040806593</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="11" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="12">
-        <v>0.01855977835960123</v>
+        <v>0.01978930538837894</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01354032921447386</v>
+        <v>0.01154576504477236</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>90</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.01549043720485259</v>
+        <v>0.0189690566061884</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P13" s="18">
-        <v>0.01511924015532539</v>
+        <v>0.02049956784444972</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S13" s="16">
-        <v>0.006141179976404798</v>
+        <v>0.006436518952462606</v>
       </c>
       <c r="T13" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="U13" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="U13" s="17" t="s">
-        <v>114</v>
-      </c>
       <c r="V13" s="18">
-        <v>0.01912220935960395</v>
+        <v>0.02033781383609201</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1998,7 +1992,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2007,7 +2001,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2016,7 +2010,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2025,7 +2019,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2034,7 +2028,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2043,7 +2037,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2052,7 +2046,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2064,130 +2058,130 @@
         <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="10">
-        <v>0.06034958932560699</v>
+        <v>0.1234775218526109</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>124</v>
-      </c>
       <c r="G16" s="12">
-        <v>0.03797573844576117</v>
+        <v>0.03861335408303223</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J16" s="14">
-        <v>0.02190082482734136</v>
+        <v>0.01891686356161523</v>
       </c>
       <c r="K16" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="L16" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="M16" s="16">
+        <v>0.04774769013419748</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="L16" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="M16" s="16">
-        <v>0.1642204053293047</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>93</v>
-      </c>
       <c r="O16" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P16" s="18">
-        <v>0.05050394785619527</v>
+        <v>0.1446299699228324</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="S16" s="16">
-        <v>0.2565826654210745</v>
+        <v>0.2598608915351437</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>66</v>
+        <v>158</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="V16" s="18">
-        <v>0.03871214813301303</v>
+        <v>0.04521985453906103</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>118</v>
-      </c>
       <c r="D17" s="10">
-        <v>0.04908570484213341</v>
+        <v>0.03848775718423879</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G17" s="12">
-        <v>0.01183376010597392</v>
+        <v>0.01260739575560954</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>133</v>
+        <v>54</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="J17" s="14">
-        <v>0.02059712887218885</v>
+        <v>0.01814200857305318</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M17" s="16">
-        <v>0.04852804668959616</v>
+        <v>0.04287933007288127</v>
       </c>
       <c r="N17" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="O17" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="O17" s="17" t="s">
-        <v>148</v>
-      </c>
       <c r="P17" s="18">
-        <v>0.03727716797834531</v>
+        <v>0.03242832762743891</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="S17" s="16">
-        <v>0.06903860593711814</v>
+        <v>0.06743578802302283</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="V17" s="18">
-        <v>0.02891709563611002</v>
+        <v>0.01520198435998974</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2196,64 +2190,64 @@
         <v>56</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D18" s="10">
-        <v>0.04582545396914934</v>
+        <v>0.03593141732189651</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G18" s="12">
-        <v>0.01167785439302441</v>
+        <v>0.01211633798898884</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J18" s="14">
-        <v>0.019380123575145</v>
+        <v>0.01757677316690185</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M18" s="16">
-        <v>0.01815473610274763</v>
+        <v>0.02565907432252906</v>
       </c>
       <c r="N18" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="O18" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="O18" s="17" t="s">
-        <v>150</v>
-      </c>
       <c r="P18" s="18">
-        <v>0.0272902349878542</v>
+        <v>0.02118448074708978</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02932681408861241</v>
+        <v>0.02856084071396158</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="V18" s="18">
-        <v>0.0197449495696456</v>
+        <v>0.01227511785427446</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2262,138 +2256,138 @@
         <v>58</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D19" s="10">
-        <v>0.03223162237168787</v>
+        <v>0.02660892521751793</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G19" s="12">
-        <v>0.01089880154561151</v>
+        <v>0.01202940331453676</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01860119051606958</v>
+        <v>0.01750267267692928</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M19" s="16">
-        <v>0.01693508011638799</v>
+        <v>0.02267444371610913</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P19" s="18">
-        <v>0.02658783647016588</v>
+        <v>0.01750596289793333</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S19" s="16">
-        <v>0.008856714919837761</v>
+        <v>0.008704386824530645</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="V19" s="18">
-        <v>0.0144779876720692</v>
+        <v>0.01152117071053283</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="D20" s="10">
+        <v>0.01071652952947328</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.01177618686227258</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.014363019704891</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.01764748420000089</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.01681714689559271</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D20" s="10">
-        <v>0.01366742164002082</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.01073632252443261</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="J20" s="14">
-        <v>0.01695114042850559</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="L20" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.0167407030610397</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.02411586986550736</v>
-      </c>
-      <c r="Q20" s="15" t="s">
-        <v>158</v>
-      </c>
       <c r="R20" s="15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="S20" s="16">
-        <v>0.00762613818578764</v>
+        <v>0.007636470585157839</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01421178588666649</v>
+        <v>0.01039657911880153</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2401,212 +2395,212 @@
         <v>54</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" s="19" t="s">
         <v>170</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2425878199317637</v>
+        <v>0.2403592234430125</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D32" s="22">
-        <v>0.1594826491136311</v>
+        <v>0.1578311754841739</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1230470174546781</v>
+        <v>0.1292537238314691</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1204899146989233</v>
+        <v>0.1277064895158408</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D35" s="22">
-        <v>0.1176795022460265</v>
+        <v>0.1126634019596501</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D36" s="22">
-        <v>0.09827236924544532</v>
+        <v>0.09659314068625811</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D37" s="22">
-        <v>0.04777305586810032</v>
+        <v>0.04598774687435147</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D38" s="22">
-        <v>0.02729805474559835</v>
+        <v>0.02555122457164112</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01544373663802463</v>
+        <v>0.01601808664514062</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D40" s="22">
-        <v>0.01410669070064895</v>
+        <v>0.01580069994308894</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01192559541215196</v>
+        <v>0.01304130008552215</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D42" s="22">
-        <v>0.007249981253485243</v>
+        <v>0.00858111433110551</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D43" s="22">
-        <v>0.007021575425401044</v>
+        <v>0.008415029600188468</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001992176578947096</v>
+        <v>0.002036825007308041</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D45" s="22">
         <v>0.0001608180212491848</v>
@@ -2614,13 +2608,13 @@
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D46" s="20" t="s">
         <v>209</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -2999,265 +2993,265 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1392524264113223</v>
+        <v>0.2066399605328701</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.1452989864767863</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0.1296455750739395</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="M9" s="16">
+        <v>0.1468623657311386</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="O9" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="P9" s="18">
+        <v>0.1235029619891796</v>
+      </c>
+      <c r="Q9" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.1710948848521781</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="J9" s="14">
-        <v>0.1331593117054012</v>
-      </c>
-      <c r="K9" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="L9" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="M9" s="16">
-        <v>0.09171491276514417</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="P9" s="18">
-        <v>0.139935454835576</v>
-      </c>
-      <c r="Q9" s="15" t="s">
-        <v>181</v>
-      </c>
       <c r="R9" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="S9" s="16">
-        <v>0.3100252327450122</v>
+        <v>0.2913746100469656</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V9" s="18">
-        <v>0.09946608252554905</v>
+        <v>0.1210390193993166</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.08285150304605321</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0.09507087864032228</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>181</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G10" s="12">
-        <v>0.08156462623465854</v>
+        <v>0.09389596853549349</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>179</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1144596202450921</v>
+        <v>0.1250189942886901</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M10" s="16">
-        <v>0.09048249403525482</v>
+        <v>0.1233732962871557</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="P10" s="18">
-        <v>0.1183485749667145</v>
+        <v>0.05158139134662674</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="S10" s="16">
-        <v>0.04782005128277532</v>
+        <v>0.0469944098728511</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V10" s="18">
-        <v>0.0816093479887855</v>
+        <v>0.09064283770012688</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D11" s="10">
-        <v>0.08313505635172158</v>
+        <v>0.06489240517169563</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G11" s="12">
-        <v>0.0627030233399741</v>
+        <v>0.06274801695677577</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>183</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J11" s="14">
-        <v>0.05812035943919357</v>
+        <v>0.0619189729472741</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M11" s="16">
-        <v>0.04741661708198391</v>
+        <v>0.05922812197022084</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="P11" s="18">
-        <v>0.06073222646920232</v>
+        <v>0.04520118183907382</v>
       </c>
       <c r="Q11" s="15" t="s">
         <v>183</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="S11" s="16">
-        <v>0.02921175649067569</v>
+        <v>0.03097763568063603</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="V11" s="18">
-        <v>0.0781419692354768</v>
+        <v>0.08441849880940791</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D12" s="10">
-        <v>0.05649637188172188</v>
+        <v>0.0431446210883983</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>183</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G12" s="12">
-        <v>0.05384478419681581</v>
+        <v>0.05885065335884555</v>
       </c>
       <c r="H12" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="J12" s="14">
+        <v>0.04913674169586828</v>
+      </c>
+      <c r="K12" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="J12" s="14">
-        <v>0.04616895712016425</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>181</v>
-      </c>
       <c r="L12" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M12" s="16">
-        <v>0.04369838233596778</v>
+        <v>0.04616072079629163</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="P12" s="18">
-        <v>0.0469691469357606</v>
+        <v>0.04413323112679974</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02323125100655058</v>
+        <v>0.02900026071546351</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="V12" s="18">
-        <v>0.07529709668562055</v>
+        <v>0.08333663015377872</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3266,64 +3260,64 @@
         <v>183</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D13" s="10">
-        <v>0.05081971977392151</v>
+        <v>0.04222481890871008</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G13" s="12">
-        <v>0.04342110262873179</v>
+        <v>0.04308083909033761</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J13" s="14">
-        <v>0.0407824914593198</v>
+        <v>0.04529896352998488</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M13" s="16">
-        <v>0.03057232719126749</v>
+        <v>0.04467805591393879</v>
       </c>
       <c r="N13" s="17" t="s">
         <v>183</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P13" s="18">
-        <v>0.0430004609592966</v>
+        <v>0.02939052634023382</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="S13" s="16">
-        <v>0.01797096034693572</v>
+        <v>0.02041282886979126</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="V13" s="18">
-        <v>0.0675726166984974</v>
+        <v>0.064285141130019</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3334,7 +3328,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3343,7 +3337,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3352,7 +3346,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3361,7 +3355,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3370,7 +3364,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3379,7 +3373,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3388,7 +3382,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3397,331 +3391,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D16" s="10">
-        <v>0.1115409444359699</v>
+        <v>0.1368181250775738</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G16" s="12">
-        <v>0.1515329274068925</v>
+        <v>0.1469888130107259</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>179</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="J16" s="14">
-        <v>0.1001882929866731</v>
+        <v>0.08905791492749617</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1892473141495734</v>
+        <v>0.185127277366473</v>
       </c>
       <c r="N16" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="O16" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.1776360331152639</v>
+      </c>
+      <c r="Q16" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="O16" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="P16" s="18">
-        <v>0.1833853788641098</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>181</v>
-      </c>
       <c r="R16" s="15" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="S16" s="16">
-        <v>0.3796136072025383</v>
+        <v>0.380134436086446</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="V16" s="18">
-        <v>0.124597634819252</v>
+        <v>0.1022018373642556</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D17" s="10">
-        <v>0.08720978976689867</v>
+        <v>0.09804194214764181</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>183</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G17" s="12">
-        <v>0.07848303723001274</v>
+        <v>0.08092523814888911</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J17" s="14">
-        <v>0.0950079987361044</v>
+        <v>0.0880934683282069</v>
       </c>
       <c r="K17" s="15" t="s">
         <v>181</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="M17" s="16">
-        <v>0.08363083412656144</v>
+        <v>0.09009999638807389</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="P17" s="18">
-        <v>0.07400608984411339</v>
+        <v>0.1072822739992631</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="S17" s="16">
-        <v>0.04630967137575969</v>
+        <v>0.04748129587328297</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="V17" s="18">
-        <v>0.09461969284643412</v>
+        <v>0.09435928111583229</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D18" s="10">
-        <v>0.08131051786433512</v>
+        <v>0.07659003609161615</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G18" s="12">
-        <v>0.05970824732799799</v>
+        <v>0.06076408951145093</v>
       </c>
       <c r="H18" s="13" t="s">
         <v>181</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J18" s="14">
-        <v>0.08704936313787474</v>
+        <v>0.07912432617720266</v>
       </c>
       <c r="K18" s="15" t="s">
         <v>179</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M18" s="16">
-        <v>0.08117949936129118</v>
+        <v>0.04167869521911091</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="P18" s="18">
-        <v>0.05827124813178192</v>
+        <v>0.05622028270048279</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="S18" s="16">
-        <v>0.02226638013052445</v>
+        <v>0.0224194828071763</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="V18" s="18">
-        <v>0.07769430273175071</v>
+        <v>0.06690079331387003</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="10">
+        <v>0.06658514816519914</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.0513928154927801</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="D19" s="10">
-        <v>0.07407702097020352</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.05559661658708433</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>189</v>
-      </c>
       <c r="I19" s="13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="J19" s="14">
-        <v>0.07162595601162643</v>
+        <v>0.07485307335926911</v>
       </c>
       <c r="K19" s="15" t="s">
         <v>183</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="M19" s="16">
-        <v>0.05316712602916375</v>
+        <v>0.04058114143537296</v>
       </c>
       <c r="N19" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="O19" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.04833695125841663</v>
+      </c>
+      <c r="Q19" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="O19" s="17" t="s">
-        <v>270</v>
-      </c>
-      <c r="P19" s="18">
-        <v>0.04359257269106682</v>
-      </c>
-      <c r="Q19" s="15" t="s">
-        <v>183</v>
-      </c>
       <c r="R19" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="S19" s="16">
-        <v>0.02098020986942196</v>
+        <v>0.02171107167132589</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="V19" s="18">
-        <v>0.04714962167893319</v>
+        <v>0.04770401792079895</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D20" s="10">
-        <v>0.04482419162256342</v>
+        <v>0.0377580603480565</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G20" s="12">
-        <v>0.0410156221922447</v>
+        <v>0.04405870138119066</v>
       </c>
       <c r="H20" s="13" t="s">
         <v>183</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J20" s="14">
-        <v>0.0629329581834452</v>
+        <v>0.06049258072147722</v>
       </c>
       <c r="K20" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="L20" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.0276435662283784</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="O20" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.04470947369022618</v>
+      </c>
+      <c r="Q20" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="L20" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="M20" s="16">
-        <v>0.04079525753739196</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>271</v>
-      </c>
-      <c r="P20" s="18">
-        <v>0.04227957569909601</v>
-      </c>
-      <c r="Q20" s="15" t="s">
+      <c r="R20" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="S20" s="16">
+        <v>0.02069776023764654</v>
+      </c>
+      <c r="T20" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="R20" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="S20" s="16">
-        <v>0.01880771468775036</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>189</v>
-      </c>
       <c r="U20" s="17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="V20" s="18">
-        <v>0.03042324605563135</v>
+        <v>0.03273513044940068</v>
       </c>
     </row>
   </sheetData>
